--- a/For Software (Certificates).xlsx
+++ b/For Software (Certificates).xlsx
@@ -5,16 +5,16 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASK MARKETING\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UH_CRM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20496" windowHeight="7752"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511" iterate="1"/>
+  <calcPr calcId="162913" iterate="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -827,7 +827,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0_ ;[Red]\-#,##0\ "/>
   </numFmts>
@@ -1131,18 +1131,6 @@
   </cellStyleXfs>
   <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1261,6 +1249,18 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1602,125 +1602,125 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L119"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="5" t="s">
+      <c r="B1" s="55"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="10">
+    <row r="2" spans="1:11" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="6">
         <f>E3*2</f>
         <v>98988000</v>
       </c>
-      <c r="J2" s="11">
+      <c r="J2" s="7">
         <f>E3</f>
         <v>49494000</v>
       </c>
-      <c r="K2" s="12"/>
-    </row>
-    <row r="3" spans="1:11" ht="62.25" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="13" t="s">
+      <c r="K2" s="8"/>
+    </row>
+    <row r="3" spans="1:11" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="10">
         <f>SUM(B5:B14)</f>
         <v>2474.6999999999998</v>
       </c>
-      <c r="E3" s="15">
+      <c r="E3" s="11">
         <f>SUM(E5:E14)</f>
         <v>49494000</v>
       </c>
-      <c r="F3" s="16"/>
-      <c r="I3" s="17" t="s">
+      <c r="F3" s="12"/>
+      <c r="I3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="J3" s="18" t="s">
+      <c r="J3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="19"/>
-    </row>
-    <row r="4" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="20" t="s">
+      <c r="K3" s="15"/>
+    </row>
+    <row r="4" spans="1:11" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="20" t="s">
+      <c r="F4" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="20" t="s">
+      <c r="G4" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="22">
+      <c r="I4" s="18">
         <f>I2-G5</f>
         <v>388000</v>
       </c>
-      <c r="J4" s="23">
+      <c r="J4" s="19">
         <f>J2-I16</f>
         <v>194000</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="24"/>
-      <c r="B5" s="25"/>
-      <c r="C5" s="26" t="s">
+    <row r="5" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="20"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27">
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23">
         <f>J4</f>
         <v>194000</v>
       </c>
-      <c r="G5" s="28">
+      <c r="G5" s="24">
         <f>SUM(H18:H142)</f>
         <v>98600000</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="29">
+    <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="25">
         <v>46122</v>
       </c>
       <c r="B6">
@@ -1730,48 +1730,48 @@
       <c r="D6">
         <v>11223</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="26">
         <v>2300000</v>
       </c>
       <c r="F6" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="31"/>
-    </row>
-    <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="29">
+      <c r="G6" s="27"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="25">
         <v>46122</v>
       </c>
       <c r="B7">
         <f t="shared" ref="B7:B13" si="0">E7/20000</f>
         <v>52</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="26">
         <v>1040000</v>
       </c>
       <c r="F7" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="31"/>
-    </row>
-    <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="29">
+      <c r="G7" s="27"/>
+    </row>
+    <row r="8" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="25">
         <v>46122</v>
       </c>
       <c r="B8">
         <f t="shared" si="0"/>
         <v>5.2</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="26">
         <v>104000</v>
       </c>
       <c r="F8" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="31"/>
-    </row>
-    <row r="9" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="29">
+      <c r="G8" s="27"/>
+    </row>
+    <row r="9" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="25">
         <v>46123</v>
       </c>
       <c r="B9">
@@ -1781,137 +1781,137 @@
       <c r="D9">
         <v>11248</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="26">
         <v>2750000</v>
       </c>
       <c r="F9" t="s">
         <v>17</v>
       </c>
-      <c r="G9" s="31"/>
-    </row>
-    <row r="10" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="29">
+      <c r="G9" s="27"/>
+    </row>
+    <row r="10" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="25">
         <v>46119</v>
       </c>
       <c r="B10">
         <f t="shared" si="0"/>
         <v>2165</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="26">
         <v>43300000</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
       </c>
-      <c r="G10" s="31"/>
-    </row>
-    <row r="11" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="29">
+      <c r="G10" s="27"/>
+    </row>
+    <row r="11" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="25">
         <v>46120</v>
       </c>
       <c r="B11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E11" s="30"/>
-      <c r="G11" s="31"/>
-    </row>
-    <row r="12" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E11" s="26"/>
+      <c r="G11" s="27"/>
+    </row>
+    <row r="12" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E12" s="30"/>
-      <c r="G12" s="31"/>
-    </row>
-    <row r="13" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E12" s="26"/>
+      <c r="G12" s="27"/>
+    </row>
+    <row r="13" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E13" s="30"/>
-      <c r="G13" s="31"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E13" s="26"/>
+      <c r="G13" s="27"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="K14" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="J15" s="32" t="s">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="J15" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="K15" s="32" t="s">
+      <c r="K15" s="28" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="H16" s="33">
+    <row r="16" spans="1:11" ht="18.600000000000001" x14ac:dyDescent="0.45">
+      <c r="H16" s="29">
         <f>SUM(H18:H147)</f>
         <v>98600000</v>
       </c>
-      <c r="I16" s="34">
+      <c r="I16" s="30">
         <f>SUM(I18:I147)</f>
         <v>49300000</v>
       </c>
-      <c r="J16" s="35">
+      <c r="J16" s="31">
         <f>SUM(J18:J147)</f>
         <v>2465</v>
       </c>
-      <c r="K16" s="36">
+      <c r="K16" s="32">
         <f>B3-J16</f>
         <v>9.6999999999998181</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A17" s="37" t="s">
+    <row r="17" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="38" t="s">
+      <c r="B17" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="37" t="s">
+      <c r="C17" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="D17" s="37" t="s">
+      <c r="D17" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="E17" s="37" t="s">
+      <c r="E17" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="F17" s="39" t="s">
+      <c r="F17" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="G17" s="39" t="s">
+      <c r="G17" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="H17" s="39" t="s">
+      <c r="H17" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="I17" s="40" t="s">
+      <c r="I17" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="J17" s="41" t="s">
+      <c r="J17" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="K17" s="42" t="s">
+      <c r="K17" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="L17" s="43" t="s">
+      <c r="L17" s="39" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1</v>
       </c>
-      <c r="B18" s="29">
+      <c r="B18" s="25">
         <v>46125</v>
       </c>
-      <c r="C18" s="32">
+      <c r="C18" s="28">
         <v>93</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" s="28" t="s">
         <v>33</v>
       </c>
       <c r="E18" t="s">
@@ -1923,14 +1923,14 @@
       <c r="G18" t="s">
         <v>36</v>
       </c>
-      <c r="H18" s="30">
+      <c r="H18" s="26">
         <v>3040000</v>
       </c>
-      <c r="I18" s="44">
+      <c r="I18" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>1520000</v>
       </c>
-      <c r="J18" s="45">
+      <c r="J18" s="41">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>76</v>
       </c>
@@ -1941,18 +1941,18 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>A18+1</f>
         <v>2</v>
       </c>
-      <c r="B19" s="29">
+      <c r="B19" s="25">
         <v>46123</v>
       </c>
-      <c r="C19" s="32">
+      <c r="C19" s="28">
         <v>96</v>
       </c>
-      <c r="D19" s="32" t="s">
+      <c r="D19" s="28" t="s">
         <v>39</v>
       </c>
       <c r="E19" t="s">
@@ -1964,14 +1964,14 @@
       <c r="G19" t="s">
         <v>42</v>
       </c>
-      <c r="H19" s="30">
+      <c r="H19" s="26">
         <v>600000</v>
       </c>
-      <c r="I19" s="44">
+      <c r="I19" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>300000</v>
       </c>
-      <c r="J19" s="45">
+      <c r="J19" s="41">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>15</v>
       </c>
@@ -1982,18 +1982,18 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20">
         <f t="shared" ref="A20:A83" si="1">A19+1</f>
         <v>3</v>
       </c>
-      <c r="B20" s="29">
+      <c r="B20" s="25">
         <v>46123</v>
       </c>
-      <c r="C20" s="32">
+      <c r="C20" s="28">
         <v>138</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D20" s="28" t="s">
         <v>39</v>
       </c>
       <c r="E20" t="s">
@@ -2005,14 +2005,14 @@
       <c r="G20" t="s">
         <v>42</v>
       </c>
-      <c r="H20" s="30">
+      <c r="H20" s="26">
         <v>600000</v>
       </c>
-      <c r="I20" s="44">
+      <c r="I20" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>300000</v>
       </c>
-      <c r="J20" s="45">
+      <c r="J20" s="41">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>15</v>
       </c>
@@ -2023,18 +2023,18 @@
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="B21" s="29">
+      <c r="B21" s="25">
         <v>46125</v>
       </c>
-      <c r="C21" s="32">
+      <c r="C21" s="28">
         <v>130</v>
       </c>
-      <c r="D21" s="32" t="s">
+      <c r="D21" s="28" t="s">
         <v>33</v>
       </c>
       <c r="E21" t="s">
@@ -2046,14 +2046,14 @@
       <c r="G21" t="s">
         <v>47</v>
       </c>
-      <c r="H21" s="30">
+      <c r="H21" s="26">
         <v>640000</v>
       </c>
-      <c r="I21" s="44">
+      <c r="I21" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>320000</v>
       </c>
-      <c r="J21" s="45">
+      <c r="J21" s="41">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>16</v>
       </c>
@@ -2064,18 +2064,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="B22" s="29">
+      <c r="B22" s="25">
         <v>46125</v>
       </c>
-      <c r="C22" s="32">
+      <c r="C22" s="28">
         <v>15</v>
       </c>
-      <c r="D22" s="32" t="s">
+      <c r="D22" s="28" t="s">
         <v>50</v>
       </c>
       <c r="E22" t="s">
@@ -2087,14 +2087,14 @@
       <c r="G22" t="s">
         <v>52</v>
       </c>
-      <c r="H22" s="30">
+      <c r="H22" s="26">
         <v>800000</v>
       </c>
-      <c r="I22" s="44">
+      <c r="I22" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>400000</v>
       </c>
-      <c r="J22" s="45">
+      <c r="J22" s="41">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>20</v>
       </c>
@@ -2105,18 +2105,18 @@
         <v>53</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="B23" s="29">
+      <c r="B23" s="25">
         <v>46130</v>
       </c>
-      <c r="C23" s="32">
+      <c r="C23" s="28">
         <v>112</v>
       </c>
-      <c r="D23" s="32" t="s">
+      <c r="D23" s="28" t="s">
         <v>39</v>
       </c>
       <c r="E23" t="s">
@@ -2128,14 +2128,14 @@
       <c r="G23" t="s">
         <v>55</v>
       </c>
-      <c r="H23" s="30">
+      <c r="H23" s="26">
         <v>960000</v>
       </c>
-      <c r="I23" s="44">
+      <c r="I23" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>480000</v>
       </c>
-      <c r="J23" s="45">
+      <c r="J23" s="41">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>24</v>
       </c>
@@ -2146,18 +2146,18 @@
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="B24" s="29">
+      <c r="B24" s="25">
         <v>46123</v>
       </c>
-      <c r="C24" s="32">
+      <c r="C24" s="28">
         <v>156</v>
       </c>
-      <c r="D24" s="32" t="s">
+      <c r="D24" s="28" t="s">
         <v>50</v>
       </c>
       <c r="E24" t="s">
@@ -2169,14 +2169,14 @@
       <c r="G24" t="s">
         <v>58</v>
       </c>
-      <c r="H24" s="30">
+      <c r="H24" s="26">
         <v>640000</v>
       </c>
-      <c r="I24" s="44">
+      <c r="I24" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>320000</v>
       </c>
-      <c r="J24" s="45">
+      <c r="J24" s="41">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>16</v>
       </c>
@@ -2187,18 +2187,18 @@
         <v>59</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="B25" s="29">
+      <c r="B25" s="25">
         <v>46123</v>
       </c>
-      <c r="C25" s="32">
+      <c r="C25" s="28">
         <v>57</v>
       </c>
-      <c r="D25" s="32" t="s">
+      <c r="D25" s="28" t="s">
         <v>60</v>
       </c>
       <c r="E25" t="s">
@@ -2210,14 +2210,14 @@
       <c r="G25" t="s">
         <v>63</v>
       </c>
-      <c r="H25" s="30">
+      <c r="H25" s="26">
         <v>200000</v>
       </c>
-      <c r="I25" s="44">
+      <c r="I25" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>100000</v>
       </c>
-      <c r="J25" s="46">
+      <c r="J25" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>5</v>
       </c>
@@ -2228,18 +2228,18 @@
         <v>65</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="B26" s="29">
+      <c r="B26" s="25">
         <v>46123</v>
       </c>
-      <c r="C26" s="32">
+      <c r="C26" s="28">
         <v>80</v>
       </c>
-      <c r="D26" s="32" t="s">
+      <c r="D26" s="28" t="s">
         <v>50</v>
       </c>
       <c r="E26" t="s">
@@ -2251,14 +2251,14 @@
       <c r="G26" t="s">
         <v>68</v>
       </c>
-      <c r="H26" s="30">
+      <c r="H26" s="26">
         <v>1000000</v>
       </c>
-      <c r="I26" s="44">
+      <c r="I26" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>500000</v>
       </c>
-      <c r="J26" s="46">
+      <c r="J26" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>25</v>
       </c>
@@ -2269,18 +2269,18 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="B27" s="29">
+      <c r="B27" s="25">
         <v>46123</v>
       </c>
-      <c r="C27" s="32">
+      <c r="C27" s="28">
         <v>154</v>
       </c>
-      <c r="D27" s="32" t="s">
+      <c r="D27" s="28" t="s">
         <v>69</v>
       </c>
       <c r="E27" t="s">
@@ -2292,14 +2292,14 @@
       <c r="G27" t="s">
         <v>71</v>
       </c>
-      <c r="H27" s="30">
+      <c r="H27" s="26">
         <v>480000</v>
       </c>
-      <c r="I27" s="44">
+      <c r="I27" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>240000</v>
       </c>
-      <c r="J27" s="46">
+      <c r="J27" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>12</v>
       </c>
@@ -2310,18 +2310,18 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="B28" s="29">
+      <c r="B28" s="25">
         <v>46123</v>
       </c>
-      <c r="C28" s="32">
+      <c r="C28" s="28">
         <v>459</v>
       </c>
-      <c r="D28" s="32" t="s">
+      <c r="D28" s="28" t="s">
         <v>33</v>
       </c>
       <c r="E28" t="s">
@@ -2333,14 +2333,14 @@
       <c r="G28" t="s">
         <v>73</v>
       </c>
-      <c r="H28" s="30">
+      <c r="H28" s="26">
         <v>200000</v>
       </c>
-      <c r="I28" s="44">
+      <c r="I28" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>100000</v>
       </c>
-      <c r="J28" s="46">
+      <c r="J28" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>5</v>
       </c>
@@ -2351,18 +2351,18 @@
         <v>65</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="B29" s="29">
+      <c r="B29" s="25">
         <v>46126</v>
       </c>
-      <c r="C29" s="32">
+      <c r="C29" s="28">
         <v>94</v>
       </c>
-      <c r="D29" s="32" t="s">
+      <c r="D29" s="28" t="s">
         <v>60</v>
       </c>
       <c r="E29" t="s">
@@ -2374,14 +2374,14 @@
       <c r="G29" t="s">
         <v>76</v>
       </c>
-      <c r="H29" s="30">
+      <c r="H29" s="26">
         <v>1240000</v>
       </c>
-      <c r="I29" s="44">
+      <c r="I29" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>620000</v>
       </c>
-      <c r="J29" s="46">
+      <c r="J29" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>31</v>
       </c>
@@ -2392,18 +2392,18 @@
         <v>77</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="B30" s="29">
+      <c r="B30" s="25">
         <v>46126</v>
       </c>
-      <c r="C30" s="32">
+      <c r="C30" s="28">
         <v>844</v>
       </c>
-      <c r="D30" s="32" t="s">
+      <c r="D30" s="28" t="s">
         <v>33</v>
       </c>
       <c r="E30" t="s">
@@ -2415,14 +2415,14 @@
       <c r="G30" t="s">
         <v>79</v>
       </c>
-      <c r="H30" s="30">
+      <c r="H30" s="26">
         <v>320000</v>
       </c>
-      <c r="I30" s="44">
+      <c r="I30" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>160000</v>
       </c>
-      <c r="J30" s="46">
+      <c r="J30" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>8</v>
       </c>
@@ -2433,18 +2433,18 @@
         <v>81</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="B31" s="29">
+      <c r="B31" s="25">
         <v>46126</v>
       </c>
-      <c r="C31" s="32" t="s">
+      <c r="C31" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="D31" s="32" t="s">
+      <c r="D31" s="28" t="s">
         <v>83</v>
       </c>
       <c r="E31" t="s">
@@ -2456,14 +2456,14 @@
       <c r="G31" t="s">
         <v>86</v>
       </c>
-      <c r="H31" s="30">
+      <c r="H31" s="26">
         <v>640000</v>
       </c>
-      <c r="I31" s="44">
+      <c r="I31" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>320000</v>
       </c>
-      <c r="J31" s="46">
+      <c r="J31" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>16</v>
       </c>
@@ -2474,18 +2474,18 @@
         <v>81</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="B32" s="29">
+      <c r="B32" s="25">
         <v>46126</v>
       </c>
-      <c r="C32" s="32">
+      <c r="C32" s="28">
         <v>100</v>
       </c>
-      <c r="D32" s="32" t="s">
+      <c r="D32" s="28" t="s">
         <v>33</v>
       </c>
       <c r="E32" t="s">
@@ -2497,14 +2497,14 @@
       <c r="G32" t="s">
         <v>89</v>
       </c>
-      <c r="H32" s="30">
+      <c r="H32" s="26">
         <v>1840000</v>
       </c>
-      <c r="I32" s="44">
+      <c r="I32" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>920000</v>
       </c>
-      <c r="J32" s="46">
+      <c r="J32" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>46</v>
       </c>
@@ -2515,18 +2515,18 @@
         <v>81</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="B33" s="29">
+      <c r="B33" s="25">
         <v>46126</v>
       </c>
-      <c r="C33" s="32">
+      <c r="C33" s="28">
         <v>29</v>
       </c>
-      <c r="D33" s="32" t="s">
+      <c r="D33" s="28" t="s">
         <v>50</v>
       </c>
       <c r="E33" t="s">
@@ -2538,14 +2538,14 @@
       <c r="G33" t="s">
         <v>68</v>
       </c>
-      <c r="H33" s="30">
+      <c r="H33" s="26">
         <v>320000</v>
       </c>
-      <c r="I33" s="44">
+      <c r="I33" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>160000</v>
       </c>
-      <c r="J33" s="46">
+      <c r="J33" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>8</v>
       </c>
@@ -2556,18 +2556,18 @@
         <v>81</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="B34" s="29">
+      <c r="B34" s="25">
         <v>46126</v>
       </c>
-      <c r="C34" s="32">
+      <c r="C34" s="28">
         <v>157</v>
       </c>
-      <c r="D34" s="32" t="s">
+      <c r="D34" s="28" t="s">
         <v>50</v>
       </c>
       <c r="E34" t="s">
@@ -2579,14 +2579,14 @@
       <c r="G34" t="s">
         <v>92</v>
       </c>
-      <c r="H34" s="30">
+      <c r="H34" s="26">
         <v>4000000</v>
       </c>
-      <c r="I34" s="44">
+      <c r="I34" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>2000000</v>
       </c>
-      <c r="J34" s="46">
+      <c r="J34" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>100</v>
       </c>
@@ -2597,18 +2597,18 @@
         <v>81</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="B35" s="29">
+      <c r="B35" s="25">
         <v>46126</v>
       </c>
-      <c r="C35" s="32">
+      <c r="C35" s="28">
         <v>665</v>
       </c>
-      <c r="D35" s="32" t="s">
+      <c r="D35" s="28" t="s">
         <v>33</v>
       </c>
       <c r="E35" t="s">
@@ -2620,14 +2620,14 @@
       <c r="G35" t="s">
         <v>95</v>
       </c>
-      <c r="H35" s="30">
+      <c r="H35" s="26">
         <v>320000</v>
       </c>
-      <c r="I35" s="44">
+      <c r="I35" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>160000</v>
       </c>
-      <c r="J35" s="46">
+      <c r="J35" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>8</v>
       </c>
@@ -2638,18 +2638,18 @@
         <v>96</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="B36" s="29">
+      <c r="B36" s="25">
         <v>46128</v>
       </c>
-      <c r="C36" s="32">
+      <c r="C36" s="28">
         <v>100</v>
       </c>
-      <c r="D36" s="32" t="s">
+      <c r="D36" s="28" t="s">
         <v>33</v>
       </c>
       <c r="E36" t="s">
@@ -2661,14 +2661,14 @@
       <c r="G36" t="s">
         <v>89</v>
       </c>
-      <c r="H36" s="30">
+      <c r="H36" s="26">
         <v>3760000</v>
       </c>
-      <c r="I36" s="44">
+      <c r="I36" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>1880000</v>
       </c>
-      <c r="J36" s="46">
+      <c r="J36" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>94</v>
       </c>
@@ -2679,18 +2679,18 @@
         <v>81</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="B37" s="29">
+      <c r="B37" s="25">
         <v>46126</v>
       </c>
-      <c r="C37" s="32">
+      <c r="C37" s="28">
         <v>41</v>
       </c>
-      <c r="D37" s="32" t="s">
+      <c r="D37" s="28" t="s">
         <v>50</v>
       </c>
       <c r="E37" t="s">
@@ -2702,14 +2702,14 @@
       <c r="G37" t="s">
         <v>58</v>
       </c>
-      <c r="H37" s="30">
+      <c r="H37" s="26">
         <v>640000</v>
       </c>
-      <c r="I37" s="44">
+      <c r="I37" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>320000</v>
       </c>
-      <c r="J37" s="46">
+      <c r="J37" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>16</v>
       </c>
@@ -2720,18 +2720,18 @@
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="B38" s="29">
+      <c r="B38" s="25">
         <v>46126</v>
       </c>
-      <c r="C38" s="32">
+      <c r="C38" s="28">
         <v>44</v>
       </c>
-      <c r="D38" s="32" t="s">
+      <c r="D38" s="28" t="s">
         <v>50</v>
       </c>
       <c r="E38" t="s">
@@ -2743,14 +2743,14 @@
       <c r="G38" t="s">
         <v>58</v>
       </c>
-      <c r="H38" s="30">
+      <c r="H38" s="26">
         <v>640000</v>
       </c>
-      <c r="I38" s="44">
+      <c r="I38" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>320000</v>
       </c>
-      <c r="J38" s="46">
+      <c r="J38" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>16</v>
       </c>
@@ -2761,18 +2761,18 @@
         <v>100</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39">
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
-      <c r="B39" s="29">
+      <c r="B39" s="25">
         <v>46126</v>
       </c>
-      <c r="C39" s="32">
+      <c r="C39" s="28">
         <v>43</v>
       </c>
-      <c r="D39" s="32" t="s">
+      <c r="D39" s="28" t="s">
         <v>50</v>
       </c>
       <c r="E39" t="s">
@@ -2784,14 +2784,14 @@
       <c r="G39" t="s">
         <v>58</v>
       </c>
-      <c r="H39" s="30">
+      <c r="H39" s="26">
         <v>640000</v>
       </c>
-      <c r="I39" s="44">
+      <c r="I39" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>320000</v>
       </c>
-      <c r="J39" s="46">
+      <c r="J39" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>16</v>
       </c>
@@ -2802,18 +2802,18 @@
         <v>100</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40">
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
-      <c r="B40" s="29">
+      <c r="B40" s="25">
         <v>46126</v>
       </c>
-      <c r="C40" s="32">
+      <c r="C40" s="28">
         <v>702</v>
       </c>
-      <c r="D40" s="32" t="s">
+      <c r="D40" s="28" t="s">
         <v>33</v>
       </c>
       <c r="E40" t="s">
@@ -2825,14 +2825,14 @@
       <c r="G40" t="s">
         <v>104</v>
       </c>
-      <c r="H40" s="30">
+      <c r="H40" s="26">
         <v>320000</v>
       </c>
-      <c r="I40" s="44">
+      <c r="I40" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>160000</v>
       </c>
-      <c r="J40" s="46">
+      <c r="J40" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>8</v>
       </c>
@@ -2843,18 +2843,18 @@
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41">
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
-      <c r="B41" s="29">
+      <c r="B41" s="25">
         <v>46126</v>
       </c>
-      <c r="C41" s="32">
+      <c r="C41" s="28">
         <v>650</v>
       </c>
-      <c r="D41" s="32" t="s">
+      <c r="D41" s="28" t="s">
         <v>33</v>
       </c>
       <c r="E41" t="s">
@@ -2866,14 +2866,14 @@
       <c r="G41" t="s">
         <v>106</v>
       </c>
-      <c r="H41" s="30">
+      <c r="H41" s="26">
         <v>320000</v>
       </c>
-      <c r="I41" s="44">
+      <c r="I41" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>160000</v>
       </c>
-      <c r="J41" s="46">
+      <c r="J41" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>8</v>
       </c>
@@ -2884,59 +2884,59 @@
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="B42" s="47">
+      <c r="B42" s="43">
         <v>46123</v>
       </c>
-      <c r="C42" s="48">
+      <c r="C42" s="44">
         <v>42</v>
       </c>
-      <c r="D42" s="48" t="s">
+      <c r="D42" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="E42" s="49" t="s">
+      <c r="E42" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="F42" s="49" t="s">
+      <c r="F42" s="45" t="s">
         <v>107</v>
       </c>
-      <c r="G42" s="49" t="s">
+      <c r="G42" s="45" t="s">
         <v>108</v>
       </c>
-      <c r="H42" s="50">
+      <c r="H42" s="46">
         <v>3400000</v>
       </c>
-      <c r="I42" s="51">
+      <c r="I42" s="47">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>1700000</v>
       </c>
-      <c r="J42" s="52">
+      <c r="J42" s="48">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>85</v>
       </c>
-      <c r="K42" s="49" t="s">
+      <c r="K42" s="45" t="s">
         <v>99</v>
       </c>
       <c r="L42" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43">
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
-      <c r="B43" s="29">
+      <c r="B43" s="25">
         <v>46128</v>
       </c>
-      <c r="C43" s="32">
+      <c r="C43" s="28">
         <v>289</v>
       </c>
-      <c r="D43" s="32" t="s">
+      <c r="D43" s="28" t="s">
         <v>110</v>
       </c>
       <c r="E43" t="s">
@@ -2948,14 +2948,14 @@
       <c r="G43" t="s">
         <v>113</v>
       </c>
-      <c r="H43" s="30">
+      <c r="H43" s="26">
         <v>480000</v>
       </c>
-      <c r="I43" s="44">
+      <c r="I43" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>240000</v>
       </c>
-      <c r="J43" s="46">
+      <c r="J43" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>12</v>
       </c>
@@ -2966,18 +2966,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44">
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
-      <c r="B44" s="29">
+      <c r="B44" s="25">
         <v>46128</v>
       </c>
-      <c r="C44" s="32">
+      <c r="C44" s="28">
         <v>289</v>
       </c>
-      <c r="D44" s="32" t="s">
+      <c r="D44" s="28" t="s">
         <v>110</v>
       </c>
       <c r="E44" t="s">
@@ -2989,14 +2989,14 @@
       <c r="G44" t="s">
         <v>113</v>
       </c>
-      <c r="H44" s="30">
+      <c r="H44" s="26">
         <v>120000</v>
       </c>
-      <c r="I44" s="44">
+      <c r="I44" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>60000</v>
       </c>
-      <c r="J44" s="46">
+      <c r="J44" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>3</v>
       </c>
@@ -3007,18 +3007,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45">
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
-      <c r="B45" s="29">
+      <c r="B45" s="25">
         <v>46127</v>
       </c>
-      <c r="C45" s="32">
+      <c r="C45" s="28">
         <v>63</v>
       </c>
-      <c r="D45" s="32" t="s">
+      <c r="D45" s="28" t="s">
         <v>110</v>
       </c>
       <c r="E45" t="s">
@@ -3030,14 +3030,14 @@
       <c r="G45" t="s">
         <v>117</v>
       </c>
-      <c r="H45" s="30">
+      <c r="H45" s="26">
         <v>320000</v>
       </c>
-      <c r="I45" s="44">
+      <c r="I45" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>160000</v>
       </c>
-      <c r="J45" s="46">
+      <c r="J45" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>8</v>
       </c>
@@ -3048,18 +3048,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46">
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
-      <c r="B46" s="29">
+      <c r="B46" s="25">
         <v>46127</v>
       </c>
-      <c r="C46" s="32">
+      <c r="C46" s="28">
         <v>266</v>
       </c>
-      <c r="D46" s="32" t="s">
+      <c r="D46" s="28" t="s">
         <v>110</v>
       </c>
       <c r="E46" t="s">
@@ -3071,14 +3071,14 @@
       <c r="G46" t="s">
         <v>119</v>
       </c>
-      <c r="H46" s="30">
+      <c r="H46" s="26">
         <v>320000</v>
       </c>
-      <c r="I46" s="44">
+      <c r="I46" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>160000</v>
       </c>
-      <c r="J46" s="46">
+      <c r="J46" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>8</v>
       </c>
@@ -3089,18 +3089,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="B47" s="29">
+      <c r="B47" s="25">
         <v>46128</v>
       </c>
-      <c r="C47" s="32">
+      <c r="C47" s="28">
         <v>52</v>
       </c>
-      <c r="D47" s="32" t="s">
+      <c r="D47" s="28" t="s">
         <v>110</v>
       </c>
       <c r="E47" t="s">
@@ -3112,14 +3112,14 @@
       <c r="G47" t="s">
         <v>68</v>
       </c>
-      <c r="H47" s="30">
+      <c r="H47" s="26">
         <v>1840000</v>
       </c>
-      <c r="I47" s="44">
+      <c r="I47" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>920000</v>
       </c>
-      <c r="J47" s="46">
+      <c r="J47" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>46</v>
       </c>
@@ -3130,18 +3130,18 @@
         <v>121</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48">
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
-      <c r="B48" s="29">
+      <c r="B48" s="25">
         <v>46128</v>
       </c>
-      <c r="C48" s="32">
+      <c r="C48" s="28">
         <v>53</v>
       </c>
-      <c r="D48" s="32" t="s">
+      <c r="D48" s="28" t="s">
         <v>110</v>
       </c>
       <c r="E48" t="s">
@@ -3153,14 +3153,14 @@
       <c r="G48" t="s">
         <v>68</v>
       </c>
-      <c r="H48" s="30">
+      <c r="H48" s="26">
         <v>1840000</v>
       </c>
-      <c r="I48" s="44">
+      <c r="I48" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>920000</v>
       </c>
-      <c r="J48" s="46">
+      <c r="J48" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>46</v>
       </c>
@@ -3171,18 +3171,18 @@
         <v>121</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49">
         <f t="shared" si="1"/>
         <v>32</v>
       </c>
-      <c r="B49" s="29">
+      <c r="B49" s="25">
         <v>46128</v>
       </c>
-      <c r="C49" s="32">
+      <c r="C49" s="28">
         <v>54</v>
       </c>
-      <c r="D49" s="32" t="s">
+      <c r="D49" s="28" t="s">
         <v>110</v>
       </c>
       <c r="E49" t="s">
@@ -3194,14 +3194,14 @@
       <c r="G49" t="s">
         <v>68</v>
       </c>
-      <c r="H49" s="30">
+      <c r="H49" s="26">
         <v>1840000</v>
       </c>
-      <c r="I49" s="44">
+      <c r="I49" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>920000</v>
       </c>
-      <c r="J49" s="46">
+      <c r="J49" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>46</v>
       </c>
@@ -3212,18 +3212,18 @@
         <v>121</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50">
         <f t="shared" si="1"/>
         <v>33</v>
       </c>
-      <c r="B50" s="29">
+      <c r="B50" s="25">
         <v>46128</v>
       </c>
-      <c r="C50" s="32">
+      <c r="C50" s="28">
         <v>1</v>
       </c>
-      <c r="D50" s="32" t="s">
+      <c r="D50" s="28" t="s">
         <v>39</v>
       </c>
       <c r="E50" t="s">
@@ -3235,14 +3235,14 @@
       <c r="G50" t="s">
         <v>126</v>
       </c>
-      <c r="H50" s="30">
+      <c r="H50" s="26">
         <v>1480000</v>
       </c>
-      <c r="I50" s="44">
+      <c r="I50" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>740000</v>
       </c>
-      <c r="J50" s="46">
+      <c r="J50" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>37</v>
       </c>
@@ -3253,18 +3253,18 @@
         <v>81</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
-      <c r="B51" s="29">
+      <c r="B51" s="25">
         <v>46128</v>
       </c>
-      <c r="C51" s="32">
+      <c r="C51" s="28">
         <v>205</v>
       </c>
-      <c r="D51" s="32" t="s">
+      <c r="D51" s="28" t="s">
         <v>60</v>
       </c>
       <c r="E51" t="s">
@@ -3276,14 +3276,14 @@
       <c r="G51" t="s">
         <v>129</v>
       </c>
-      <c r="H51" s="30">
+      <c r="H51" s="26">
         <v>200000</v>
       </c>
-      <c r="I51" s="44">
+      <c r="I51" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>100000</v>
       </c>
-      <c r="J51" s="46">
+      <c r="J51" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>5</v>
       </c>
@@ -3294,18 +3294,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52">
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
-      <c r="B52" s="29">
+      <c r="B52" s="25">
         <v>46128</v>
       </c>
-      <c r="C52" s="32">
+      <c r="C52" s="28">
         <v>85</v>
       </c>
-      <c r="D52" s="32" t="s">
+      <c r="D52" s="28" t="s">
         <v>130</v>
       </c>
       <c r="E52" t="s">
@@ -3317,14 +3317,14 @@
       <c r="G52" t="s">
         <v>133</v>
       </c>
-      <c r="H52" s="30">
+      <c r="H52" s="26">
         <v>80000</v>
       </c>
-      <c r="I52" s="44">
+      <c r="I52" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>40000</v>
       </c>
-      <c r="J52" s="46">
+      <c r="J52" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>2</v>
       </c>
@@ -3335,18 +3335,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53">
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
-      <c r="B53" s="29">
+      <c r="B53" s="25">
         <v>46128</v>
       </c>
-      <c r="C53" s="32">
+      <c r="C53" s="28">
         <v>85</v>
       </c>
-      <c r="D53" s="32" t="s">
+      <c r="D53" s="28" t="s">
         <v>130</v>
       </c>
       <c r="E53" t="s">
@@ -3358,14 +3358,14 @@
       <c r="G53" t="s">
         <v>133</v>
       </c>
-      <c r="H53" s="30">
+      <c r="H53" s="26">
         <v>120000</v>
       </c>
-      <c r="I53" s="44">
+      <c r="I53" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>60000</v>
       </c>
-      <c r="J53" s="46">
+      <c r="J53" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>3</v>
       </c>
@@ -3376,18 +3376,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54">
         <f t="shared" si="1"/>
         <v>37</v>
       </c>
-      <c r="B54" s="29">
+      <c r="B54" s="25">
         <v>46128</v>
       </c>
-      <c r="C54" s="32">
+      <c r="C54" s="28">
         <v>548</v>
       </c>
-      <c r="D54" s="32" t="s">
+      <c r="D54" s="28" t="s">
         <v>33</v>
       </c>
       <c r="E54" t="s">
@@ -3399,14 +3399,14 @@
       <c r="G54" t="s">
         <v>133</v>
       </c>
-      <c r="H54" s="30">
+      <c r="H54" s="26">
         <v>320000</v>
       </c>
-      <c r="I54" s="44">
+      <c r="I54" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>160000</v>
       </c>
-      <c r="J54" s="46">
+      <c r="J54" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>8</v>
       </c>
@@ -3417,18 +3417,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55">
         <f t="shared" si="1"/>
         <v>38</v>
       </c>
-      <c r="B55" s="29">
+      <c r="B55" s="25">
         <v>46130</v>
       </c>
-      <c r="C55" s="32">
+      <c r="C55" s="28">
         <v>542</v>
       </c>
-      <c r="D55" s="32" t="s">
+      <c r="D55" s="28" t="s">
         <v>33</v>
       </c>
       <c r="E55" t="s">
@@ -3440,14 +3440,14 @@
       <c r="G55" t="s">
         <v>137</v>
       </c>
-      <c r="H55" s="30">
+      <c r="H55" s="26">
         <v>240000</v>
       </c>
-      <c r="I55" s="44">
+      <c r="I55" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>120000</v>
       </c>
-      <c r="J55" s="46">
+      <c r="J55" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>6</v>
       </c>
@@ -3458,59 +3458,59 @@
         <v>49</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56">
         <f t="shared" si="1"/>
         <v>39</v>
       </c>
-      <c r="B56" s="53">
+      <c r="B56" s="49">
         <v>46137</v>
       </c>
-      <c r="C56" s="54">
+      <c r="C56" s="50">
         <v>334</v>
       </c>
-      <c r="D56" s="54" t="s">
+      <c r="D56" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="E56" s="12" t="s">
+      <c r="E56" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="F56" s="12" t="s">
+      <c r="F56" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="G56" s="12" t="s">
+      <c r="G56" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="H56" s="55">
+      <c r="H56" s="51">
         <v>120000</v>
       </c>
-      <c r="I56" s="56">
+      <c r="I56" s="52">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>60000</v>
       </c>
-      <c r="J56" s="57">
+      <c r="J56" s="53">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>3</v>
       </c>
-      <c r="K56" s="12" t="s">
+      <c r="K56" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="L56" s="12" t="s">
+      <c r="L56" s="8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="B57" s="29">
+      <c r="B57" s="25">
         <v>46130</v>
       </c>
-      <c r="C57" s="32">
+      <c r="C57" s="28">
         <v>334</v>
       </c>
-      <c r="D57" s="32" t="s">
+      <c r="D57" s="28" t="s">
         <v>130</v>
       </c>
       <c r="E57" t="s">
@@ -3522,14 +3522,14 @@
       <c r="G57" t="s">
         <v>139</v>
       </c>
-      <c r="H57" s="30">
+      <c r="H57" s="26">
         <v>120000</v>
       </c>
-      <c r="I57" s="44">
+      <c r="I57" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>60000</v>
       </c>
-      <c r="J57" s="46">
+      <c r="J57" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>3</v>
       </c>
@@ -3540,18 +3540,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58">
         <f t="shared" si="1"/>
         <v>41</v>
       </c>
-      <c r="B58" s="29">
+      <c r="B58" s="25">
         <v>46130</v>
       </c>
-      <c r="C58" s="32">
+      <c r="C58" s="28">
         <v>358</v>
       </c>
-      <c r="D58" s="32" t="s">
+      <c r="D58" s="28" t="s">
         <v>33</v>
       </c>
       <c r="E58" t="s">
@@ -3563,14 +3563,14 @@
       <c r="G58" t="s">
         <v>117</v>
       </c>
-      <c r="H58" s="30">
+      <c r="H58" s="26">
         <v>1200000</v>
       </c>
-      <c r="I58" s="44">
+      <c r="I58" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>600000</v>
       </c>
-      <c r="J58" s="46">
+      <c r="J58" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>30</v>
       </c>
@@ -3581,18 +3581,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="B59" s="29">
+      <c r="B59" s="25">
         <v>46129</v>
       </c>
-      <c r="C59" s="32">
+      <c r="C59" s="28">
         <v>797</v>
       </c>
-      <c r="D59" s="32" t="s">
+      <c r="D59" s="28" t="s">
         <v>33</v>
       </c>
       <c r="E59" t="s">
@@ -3604,14 +3604,14 @@
       <c r="G59" t="s">
         <v>144</v>
       </c>
-      <c r="H59" s="30">
+      <c r="H59" s="26">
         <v>3640000</v>
       </c>
-      <c r="I59" s="44">
+      <c r="I59" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>1820000</v>
       </c>
-      <c r="J59" s="46">
+      <c r="J59" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>91</v>
       </c>
@@ -3622,18 +3622,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60">
         <f t="shared" si="1"/>
         <v>43</v>
       </c>
-      <c r="B60" s="29">
+      <c r="B60" s="25">
         <v>46130</v>
       </c>
-      <c r="C60" s="32">
+      <c r="C60" s="28">
         <v>25</v>
       </c>
-      <c r="D60" s="32" t="s">
+      <c r="D60" s="28" t="s">
         <v>39</v>
       </c>
       <c r="E60" t="s">
@@ -3645,14 +3645,14 @@
       <c r="G60" t="s">
         <v>146</v>
       </c>
-      <c r="H60" s="30">
+      <c r="H60" s="26">
         <v>1320000</v>
       </c>
-      <c r="I60" s="44">
+      <c r="I60" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>660000</v>
       </c>
-      <c r="J60" s="46">
+      <c r="J60" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>33</v>
       </c>
@@ -3663,31 +3663,31 @@
         <v>81</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61">
         <f t="shared" si="1"/>
         <v>44</v>
       </c>
-      <c r="B61" s="29">
+      <c r="B61" s="25">
         <v>46128</v>
       </c>
-      <c r="C61" s="32">
+      <c r="C61" s="28">
         <v>146</v>
       </c>
-      <c r="D61" s="32" t="s">
+      <c r="D61" s="28" t="s">
         <v>39</v>
       </c>
       <c r="E61" t="s">
         <v>87</v>
       </c>
-      <c r="H61" s="30">
+      <c r="H61" s="26">
         <v>1840000</v>
       </c>
-      <c r="I61" s="44">
+      <c r="I61" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>920000</v>
       </c>
-      <c r="J61" s="46">
+      <c r="J61" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>46</v>
       </c>
@@ -3698,18 +3698,18 @@
         <v>148</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62">
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
-      <c r="B62" s="29">
+      <c r="B62" s="25">
         <v>46133</v>
       </c>
-      <c r="C62" s="32">
+      <c r="C62" s="28">
         <v>113</v>
       </c>
-      <c r="D62" s="32" t="s">
+      <c r="D62" s="28" t="s">
         <v>33</v>
       </c>
       <c r="E62" t="s">
@@ -3721,14 +3721,14 @@
       <c r="G62" t="s">
         <v>150</v>
       </c>
-      <c r="H62" s="30">
+      <c r="H62" s="26">
         <v>1000000</v>
       </c>
-      <c r="I62" s="44">
+      <c r="I62" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>500000</v>
       </c>
-      <c r="J62" s="46">
+      <c r="J62" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>25</v>
       </c>
@@ -3739,18 +3739,18 @@
         <v>151</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63">
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
-      <c r="B63" s="29">
+      <c r="B63" s="25">
         <v>46132</v>
       </c>
-      <c r="C63" s="32">
+      <c r="C63" s="28">
         <v>170</v>
       </c>
-      <c r="D63" s="32" t="s">
+      <c r="D63" s="28" t="s">
         <v>50</v>
       </c>
       <c r="E63" t="s">
@@ -3762,14 +3762,14 @@
       <c r="G63" t="s">
         <v>153</v>
       </c>
-      <c r="H63" s="30">
+      <c r="H63" s="26">
         <v>120000</v>
       </c>
-      <c r="I63" s="44">
+      <c r="I63" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>60000</v>
       </c>
-      <c r="J63" s="46">
+      <c r="J63" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>3</v>
       </c>
@@ -3780,18 +3780,18 @@
         <v>154</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64">
         <f t="shared" si="1"/>
         <v>47</v>
       </c>
-      <c r="B64" s="29">
+      <c r="B64" s="25">
         <v>46132</v>
       </c>
-      <c r="C64" s="32">
+      <c r="C64" s="28">
         <v>266</v>
       </c>
-      <c r="D64" s="32" t="s">
+      <c r="D64" s="28" t="s">
         <v>33</v>
       </c>
       <c r="E64" t="s">
@@ -3803,14 +3803,14 @@
       <c r="G64" t="s">
         <v>156</v>
       </c>
-      <c r="H64" s="30">
+      <c r="H64" s="26">
         <v>320000</v>
       </c>
-      <c r="I64" s="44">
+      <c r="I64" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>160000</v>
       </c>
-      <c r="J64" s="46">
+      <c r="J64" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>8</v>
       </c>
@@ -3821,18 +3821,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65">
         <f t="shared" si="1"/>
         <v>48</v>
       </c>
-      <c r="B65" s="29">
+      <c r="B65" s="25">
         <v>46132</v>
       </c>
-      <c r="C65" s="32">
+      <c r="C65" s="28">
         <v>466</v>
       </c>
-      <c r="D65" s="32" t="s">
+      <c r="D65" s="28" t="s">
         <v>60</v>
       </c>
       <c r="E65" t="s">
@@ -3844,14 +3844,14 @@
       <c r="G65" t="s">
         <v>158</v>
       </c>
-      <c r="H65" s="30">
+      <c r="H65" s="26">
         <v>200000</v>
       </c>
-      <c r="I65" s="44">
+      <c r="I65" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>100000</v>
       </c>
-      <c r="J65" s="46">
+      <c r="J65" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>5</v>
       </c>
@@ -3862,18 +3862,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66">
         <f t="shared" si="1"/>
         <v>49</v>
       </c>
-      <c r="B66" s="29">
+      <c r="B66" s="25">
         <v>46134</v>
       </c>
-      <c r="C66" s="32">
+      <c r="C66" s="28">
         <v>185</v>
       </c>
-      <c r="D66" s="32" t="s">
+      <c r="D66" s="28" t="s">
         <v>110</v>
       </c>
       <c r="E66" t="s">
@@ -3885,14 +3885,14 @@
       <c r="G66" t="s">
         <v>160</v>
       </c>
-      <c r="H66" s="30">
+      <c r="H66" s="26">
         <v>200000</v>
       </c>
-      <c r="I66" s="44">
+      <c r="I66" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>100000</v>
       </c>
-      <c r="J66" s="46">
+      <c r="J66" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>5</v>
       </c>
@@ -3903,18 +3903,18 @@
         <v>81</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="B67" s="29">
+      <c r="B67" s="25">
         <v>46135</v>
       </c>
-      <c r="C67" s="32">
+      <c r="C67" s="28">
         <v>286</v>
       </c>
-      <c r="D67" s="32" t="s">
+      <c r="D67" s="28" t="s">
         <v>33</v>
       </c>
       <c r="E67" t="s">
@@ -3926,14 +3926,14 @@
       <c r="G67" t="s">
         <v>162</v>
       </c>
-      <c r="H67" s="30">
+      <c r="H67" s="26">
         <v>640000</v>
       </c>
-      <c r="I67" s="44">
+      <c r="I67" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>320000</v>
       </c>
-      <c r="J67" s="46">
+      <c r="J67" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>16</v>
       </c>
@@ -3944,18 +3944,18 @@
         <v>81</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68">
         <f t="shared" si="1"/>
         <v>51</v>
       </c>
-      <c r="B68" s="29">
+      <c r="B68" s="25">
         <v>46134</v>
       </c>
-      <c r="C68" s="32">
+      <c r="C68" s="28">
         <v>844</v>
       </c>
-      <c r="D68" s="32" t="s">
+      <c r="D68" s="28" t="s">
         <v>33</v>
       </c>
       <c r="E68" t="s">
@@ -3967,14 +3967,14 @@
       <c r="G68" t="s">
         <v>79</v>
       </c>
-      <c r="H68" s="30">
+      <c r="H68" s="26">
         <v>320000</v>
       </c>
-      <c r="I68" s="44">
+      <c r="I68" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>160000</v>
       </c>
-      <c r="J68" s="46">
+      <c r="J68" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>8</v>
       </c>
@@ -3985,18 +3985,18 @@
         <v>81</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69">
         <f t="shared" si="1"/>
         <v>52</v>
       </c>
-      <c r="B69" s="29">
+      <c r="B69" s="25">
         <v>46135</v>
       </c>
-      <c r="C69" s="32">
+      <c r="C69" s="28">
         <v>59</v>
       </c>
-      <c r="D69" s="32" t="s">
+      <c r="D69" s="28" t="s">
         <v>110</v>
       </c>
       <c r="E69" t="s">
@@ -4008,14 +4008,14 @@
       <c r="G69" t="s">
         <v>165</v>
       </c>
-      <c r="H69" s="30">
+      <c r="H69" s="26">
         <v>3240000</v>
       </c>
-      <c r="I69" s="44">
+      <c r="I69" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>1620000</v>
       </c>
-      <c r="J69" s="46">
+      <c r="J69" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>81</v>
       </c>
@@ -4026,18 +4026,18 @@
         <v>81</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70">
         <f t="shared" si="1"/>
         <v>53</v>
       </c>
-      <c r="B70" s="29">
+      <c r="B70" s="25">
         <v>46134</v>
       </c>
-      <c r="C70" s="32">
+      <c r="C70" s="28">
         <v>17</v>
       </c>
-      <c r="D70" s="32" t="s">
+      <c r="D70" s="28" t="s">
         <v>110</v>
       </c>
       <c r="E70" t="s">
@@ -4049,14 +4049,14 @@
       <c r="G70" t="s">
         <v>167</v>
       </c>
-      <c r="H70" s="30">
+      <c r="H70" s="26">
         <v>1000000</v>
       </c>
-      <c r="I70" s="44">
+      <c r="I70" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>500000</v>
       </c>
-      <c r="J70" s="46">
+      <c r="J70" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>25</v>
       </c>
@@ -4067,18 +4067,18 @@
         <v>168</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71">
         <f t="shared" si="1"/>
         <v>54</v>
       </c>
-      <c r="B71" s="29">
+      <c r="B71" s="25">
         <v>46134</v>
       </c>
-      <c r="C71" s="32">
+      <c r="C71" s="28">
         <v>164</v>
       </c>
-      <c r="D71" s="32" t="s">
+      <c r="D71" s="28" t="s">
         <v>110</v>
       </c>
       <c r="E71" t="s">
@@ -4090,14 +4090,14 @@
       <c r="G71" t="s">
         <v>170</v>
       </c>
-      <c r="H71" s="30">
+      <c r="H71" s="26">
         <v>320000</v>
       </c>
-      <c r="I71" s="44">
+      <c r="I71" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>160000</v>
       </c>
-      <c r="J71" s="46">
+      <c r="J71" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>8</v>
       </c>
@@ -4108,18 +4108,18 @@
         <v>100</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72">
         <f t="shared" si="1"/>
         <v>55</v>
       </c>
-      <c r="B72" s="29">
+      <c r="B72" s="25">
         <v>46134</v>
       </c>
-      <c r="C72" s="32">
+      <c r="C72" s="28">
         <v>432</v>
       </c>
-      <c r="D72" s="32" t="s">
+      <c r="D72" s="28" t="s">
         <v>33</v>
       </c>
       <c r="E72" t="s">
@@ -4131,14 +4131,14 @@
       <c r="G72" t="s">
         <v>172</v>
       </c>
-      <c r="H72" s="30">
+      <c r="H72" s="26">
         <v>320000</v>
       </c>
-      <c r="I72" s="44">
+      <c r="I72" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>160000</v>
       </c>
-      <c r="J72" s="46">
+      <c r="J72" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>8</v>
       </c>
@@ -4149,18 +4149,18 @@
         <v>100</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73">
         <f t="shared" si="1"/>
         <v>56</v>
       </c>
-      <c r="B73" s="29">
+      <c r="B73" s="25">
         <v>46134</v>
       </c>
-      <c r="C73" s="32">
+      <c r="C73" s="28">
         <v>573</v>
       </c>
-      <c r="D73" s="32" t="s">
+      <c r="D73" s="28" t="s">
         <v>33</v>
       </c>
       <c r="E73" t="s">
@@ -4172,14 +4172,14 @@
       <c r="G73" t="s">
         <v>174</v>
       </c>
-      <c r="H73" s="30">
+      <c r="H73" s="26">
         <v>1320000</v>
       </c>
-      <c r="I73" s="44">
+      <c r="I73" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>660000</v>
       </c>
-      <c r="J73" s="46">
+      <c r="J73" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>33</v>
       </c>
@@ -4190,18 +4190,18 @@
         <v>100</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74">
         <f t="shared" si="1"/>
         <v>57</v>
       </c>
-      <c r="B74" s="29">
+      <c r="B74" s="25">
         <v>46134</v>
       </c>
-      <c r="C74" s="32">
+      <c r="C74" s="28">
         <v>33</v>
       </c>
-      <c r="D74" s="32" t="s">
+      <c r="D74" s="28" t="s">
         <v>50</v>
       </c>
       <c r="E74" t="s">
@@ -4213,14 +4213,14 @@
       <c r="G74" t="s">
         <v>176</v>
       </c>
-      <c r="H74" s="30">
+      <c r="H74" s="26">
         <v>320000</v>
       </c>
-      <c r="I74" s="44">
+      <c r="I74" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>160000</v>
       </c>
-      <c r="J74" s="46">
+      <c r="J74" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>8</v>
       </c>
@@ -4231,18 +4231,18 @@
         <v>100</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75">
         <f t="shared" si="1"/>
         <v>58</v>
       </c>
-      <c r="B75" s="29">
+      <c r="B75" s="25">
         <v>46134</v>
       </c>
-      <c r="C75" s="32">
+      <c r="C75" s="28">
         <v>432</v>
       </c>
-      <c r="D75" s="32" t="s">
+      <c r="D75" s="28" t="s">
         <v>60</v>
       </c>
       <c r="E75" t="s">
@@ -4254,14 +4254,14 @@
       <c r="G75" t="s">
         <v>178</v>
       </c>
-      <c r="H75" s="30">
+      <c r="H75" s="26">
         <v>80000</v>
       </c>
-      <c r="I75" s="44">
+      <c r="I75" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>40000</v>
       </c>
-      <c r="J75" s="46">
+      <c r="J75" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>2</v>
       </c>
@@ -4272,18 +4272,18 @@
         <v>100</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76">
         <f t="shared" si="1"/>
         <v>59</v>
       </c>
-      <c r="B76" s="29">
+      <c r="B76" s="25">
         <v>46134</v>
       </c>
-      <c r="C76" s="32">
+      <c r="C76" s="28">
         <v>243</v>
       </c>
-      <c r="D76" s="32" t="s">
+      <c r="D76" s="28" t="s">
         <v>33</v>
       </c>
       <c r="E76" t="s">
@@ -4295,14 +4295,14 @@
       <c r="G76" t="s">
         <v>180</v>
       </c>
-      <c r="H76" s="30">
+      <c r="H76" s="26">
         <v>320000</v>
       </c>
-      <c r="I76" s="44">
+      <c r="I76" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>160000</v>
       </c>
-      <c r="J76" s="46">
+      <c r="J76" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>8</v>
       </c>
@@ -4313,18 +4313,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="B77" s="29">
+      <c r="B77" s="25">
         <v>46135</v>
       </c>
-      <c r="C77" s="32">
+      <c r="C77" s="28">
         <v>205</v>
       </c>
-      <c r="D77" s="32" t="s">
+      <c r="D77" s="28" t="s">
         <v>110</v>
       </c>
       <c r="E77" t="s">
@@ -4336,14 +4336,14 @@
       <c r="G77" t="s">
         <v>183</v>
       </c>
-      <c r="H77" s="30">
+      <c r="H77" s="26">
         <v>160000</v>
       </c>
-      <c r="I77" s="44">
+      <c r="I77" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>80000</v>
       </c>
-      <c r="J77" s="46">
+      <c r="J77" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>4</v>
       </c>
@@ -4354,18 +4354,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78">
         <f t="shared" si="1"/>
         <v>61</v>
       </c>
-      <c r="B78" s="29">
+      <c r="B78" s="25">
         <v>46135</v>
       </c>
-      <c r="C78" s="32">
+      <c r="C78" s="28">
         <v>206</v>
       </c>
-      <c r="D78" s="32" t="s">
+      <c r="D78" s="28" t="s">
         <v>110</v>
       </c>
       <c r="E78" t="s">
@@ -4377,14 +4377,14 @@
       <c r="G78" t="s">
         <v>183</v>
       </c>
-      <c r="H78" s="30">
+      <c r="H78" s="26">
         <v>160000</v>
       </c>
-      <c r="I78" s="44">
+      <c r="I78" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>80000</v>
       </c>
-      <c r="J78" s="46">
+      <c r="J78" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>4</v>
       </c>
@@ -4395,18 +4395,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79">
         <f t="shared" si="1"/>
         <v>62</v>
       </c>
-      <c r="B79" s="29">
+      <c r="B79" s="25">
         <v>46134</v>
       </c>
-      <c r="C79" s="32">
+      <c r="C79" s="28">
         <v>15</v>
       </c>
-      <c r="D79" s="32" t="s">
+      <c r="D79" s="28" t="s">
         <v>50</v>
       </c>
       <c r="E79" t="s">
@@ -4418,14 +4418,14 @@
       <c r="G79" t="s">
         <v>52</v>
       </c>
-      <c r="H79" s="30">
+      <c r="H79" s="26">
         <v>160000</v>
       </c>
-      <c r="I79" s="44">
+      <c r="I79" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>80000</v>
       </c>
-      <c r="J79" s="46">
+      <c r="J79" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>4</v>
       </c>
@@ -4436,18 +4436,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80">
         <f t="shared" si="1"/>
         <v>63</v>
       </c>
-      <c r="B80" s="29">
+      <c r="B80" s="25">
         <v>46134</v>
       </c>
-      <c r="C80" s="32">
+      <c r="C80" s="28">
         <v>234</v>
       </c>
-      <c r="D80" s="32" t="s">
+      <c r="D80" s="28" t="s">
         <v>60</v>
       </c>
       <c r="E80" t="s">
@@ -4459,14 +4459,14 @@
       <c r="G80" t="s">
         <v>187</v>
       </c>
-      <c r="H80" s="30">
+      <c r="H80" s="26">
         <v>1840000</v>
       </c>
-      <c r="I80" s="44">
+      <c r="I80" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>920000</v>
       </c>
-      <c r="J80" s="46">
+      <c r="J80" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>46</v>
       </c>
@@ -4477,18 +4477,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81">
         <f t="shared" si="1"/>
         <v>64</v>
       </c>
-      <c r="B81" s="29">
+      <c r="B81" s="25">
         <v>46133</v>
       </c>
-      <c r="C81" s="32">
+      <c r="C81" s="28">
         <v>126</v>
       </c>
-      <c r="D81" s="32" t="s">
+      <c r="D81" s="28" t="s">
         <v>33</v>
       </c>
       <c r="E81" t="s">
@@ -4500,14 +4500,14 @@
       <c r="G81" t="s">
         <v>189</v>
       </c>
-      <c r="H81" s="30">
+      <c r="H81" s="26">
         <v>1040000</v>
       </c>
-      <c r="I81" s="44">
+      <c r="I81" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>520000</v>
       </c>
-      <c r="J81" s="46">
+      <c r="J81" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>26</v>
       </c>
@@ -4518,18 +4518,18 @@
         <v>151</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82">
         <f t="shared" si="1"/>
         <v>65</v>
       </c>
-      <c r="B82" s="29">
+      <c r="B82" s="25">
         <v>46135</v>
       </c>
-      <c r="C82" s="32">
+      <c r="C82" s="28">
         <v>16</v>
       </c>
-      <c r="D82" s="32" t="s">
+      <c r="D82" s="28" t="s">
         <v>33</v>
       </c>
       <c r="E82" t="s">
@@ -4541,14 +4541,14 @@
       <c r="G82" t="s">
         <v>191</v>
       </c>
-      <c r="H82" s="30">
+      <c r="H82" s="26">
         <v>240000</v>
       </c>
-      <c r="I82" s="44">
+      <c r="I82" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>120000</v>
       </c>
-      <c r="J82" s="46">
+      <c r="J82" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>6</v>
       </c>
@@ -4559,18 +4559,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83">
         <f t="shared" si="1"/>
         <v>66</v>
       </c>
-      <c r="B83" s="29">
+      <c r="B83" s="25">
         <v>46136</v>
       </c>
-      <c r="C83" s="32">
+      <c r="C83" s="28">
         <v>11</v>
       </c>
-      <c r="D83" s="32" t="s">
+      <c r="D83" s="28" t="s">
         <v>50</v>
       </c>
       <c r="E83" t="s">
@@ -4582,14 +4582,14 @@
       <c r="G83" t="s">
         <v>137</v>
       </c>
-      <c r="H83" s="30">
+      <c r="H83" s="26">
         <v>240000</v>
       </c>
-      <c r="I83" s="44">
+      <c r="I83" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>120000</v>
       </c>
-      <c r="J83" s="46">
+      <c r="J83" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>6</v>
       </c>
@@ -4600,18 +4600,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84">
         <f t="shared" ref="A84:A96" si="2">A83+1</f>
         <v>67</v>
       </c>
-      <c r="B84" s="29">
+      <c r="B84" s="25">
         <v>46136</v>
       </c>
-      <c r="C84" s="32">
+      <c r="C84" s="28">
         <v>71</v>
       </c>
-      <c r="D84" s="32" t="s">
+      <c r="D84" s="28" t="s">
         <v>39</v>
       </c>
       <c r="E84" t="s">
@@ -4623,14 +4623,14 @@
       <c r="G84" t="s">
         <v>195</v>
       </c>
-      <c r="H84" s="30">
+      <c r="H84" s="26">
         <v>680000</v>
       </c>
-      <c r="I84" s="44">
+      <c r="I84" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>340000</v>
       </c>
-      <c r="J84" s="46">
+      <c r="J84" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>17</v>
       </c>
@@ -4641,18 +4641,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85">
         <f t="shared" si="2"/>
         <v>68</v>
       </c>
-      <c r="B85" s="29">
+      <c r="B85" s="25">
         <v>46136</v>
       </c>
-      <c r="C85" s="32">
+      <c r="C85" s="28">
         <v>184</v>
       </c>
-      <c r="D85" s="32" t="s">
+      <c r="D85" s="28" t="s">
         <v>110</v>
       </c>
       <c r="E85" t="s">
@@ -4664,14 +4664,14 @@
       <c r="G85" t="s">
         <v>198</v>
       </c>
-      <c r="H85" s="30">
+      <c r="H85" s="26">
         <v>400000</v>
       </c>
-      <c r="I85" s="44">
+      <c r="I85" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>200000</v>
       </c>
-      <c r="J85" s="46">
+      <c r="J85" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>10</v>
       </c>
@@ -4682,18 +4682,18 @@
         <v>199</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86">
         <f t="shared" si="2"/>
         <v>69</v>
       </c>
-      <c r="B86" s="29">
+      <c r="B86" s="25">
         <v>46137</v>
       </c>
-      <c r="C86" s="32">
+      <c r="C86" s="28">
         <v>29</v>
       </c>
-      <c r="D86" s="32" t="s">
+      <c r="D86" s="28" t="s">
         <v>60</v>
       </c>
       <c r="E86" t="s">
@@ -4705,14 +4705,14 @@
       <c r="G86" t="s">
         <v>201</v>
       </c>
-      <c r="H86" s="30">
+      <c r="H86" s="26">
         <v>40000</v>
       </c>
-      <c r="I86" s="44">
+      <c r="I86" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>20000</v>
       </c>
-      <c r="J86" s="46">
+      <c r="J86" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>1</v>
       </c>
@@ -4723,18 +4723,18 @@
         <v>100</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87">
         <f t="shared" si="2"/>
         <v>70</v>
       </c>
-      <c r="B87" s="29">
+      <c r="B87" s="25">
         <v>46137</v>
       </c>
-      <c r="C87" s="32">
+      <c r="C87" s="28">
         <v>162</v>
       </c>
-      <c r="D87" s="32" t="s">
+      <c r="D87" s="28" t="s">
         <v>50</v>
       </c>
       <c r="E87" t="s">
@@ -4746,14 +4746,14 @@
       <c r="G87" t="s">
         <v>203</v>
       </c>
-      <c r="H87" s="30">
+      <c r="H87" s="26">
         <v>680000</v>
       </c>
-      <c r="I87" s="44">
+      <c r="I87" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>340000</v>
       </c>
-      <c r="J87" s="46">
+      <c r="J87" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>17</v>
       </c>
@@ -4764,18 +4764,18 @@
         <v>100</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88">
         <f t="shared" si="2"/>
         <v>71</v>
       </c>
-      <c r="B88" s="29">
+      <c r="B88" s="25">
         <v>46136</v>
       </c>
-      <c r="C88" s="32">
+      <c r="C88" s="28">
         <v>138</v>
       </c>
-      <c r="D88" s="32" t="s">
+      <c r="D88" s="28" t="s">
         <v>204</v>
       </c>
       <c r="E88" t="s">
@@ -4787,14 +4787,14 @@
       <c r="G88" t="s">
         <v>207</v>
       </c>
-      <c r="H88" s="30">
+      <c r="H88" s="26">
         <v>320000</v>
       </c>
-      <c r="I88" s="44">
+      <c r="I88" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>160000</v>
       </c>
-      <c r="J88" s="46">
+      <c r="J88" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>8</v>
       </c>
@@ -4805,18 +4805,18 @@
         <v>96</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89">
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
-      <c r="B89" s="29">
+      <c r="B89" s="25">
         <v>46136</v>
       </c>
-      <c r="C89" s="32">
+      <c r="C89" s="28">
         <v>8</v>
       </c>
-      <c r="D89" s="32" t="s">
+      <c r="D89" s="28" t="s">
         <v>60</v>
       </c>
       <c r="E89" t="s">
@@ -4828,14 +4828,14 @@
       <c r="G89" t="s">
         <v>209</v>
       </c>
-      <c r="H89" s="30">
+      <c r="H89" s="26">
         <v>200000</v>
       </c>
-      <c r="I89" s="44">
+      <c r="I89" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>100000</v>
       </c>
-      <c r="J89" s="46">
+      <c r="J89" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>5</v>
       </c>
@@ -4846,18 +4846,18 @@
         <v>81</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90">
         <f t="shared" si="2"/>
         <v>73</v>
       </c>
-      <c r="B90" s="29">
+      <c r="B90" s="25">
         <v>46136</v>
       </c>
-      <c r="C90" s="32">
+      <c r="C90" s="28">
         <v>237</v>
       </c>
-      <c r="D90" s="32" t="s">
+      <c r="D90" s="28" t="s">
         <v>50</v>
       </c>
       <c r="E90" t="s">
@@ -4869,14 +4869,14 @@
       <c r="G90" t="s">
         <v>211</v>
       </c>
-      <c r="H90" s="30">
+      <c r="H90" s="26">
         <v>720000</v>
       </c>
-      <c r="I90" s="44">
+      <c r="I90" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>360000</v>
       </c>
-      <c r="J90" s="46">
+      <c r="J90" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>18</v>
       </c>
@@ -4887,18 +4887,18 @@
         <v>81</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91">
         <f t="shared" si="2"/>
         <v>74</v>
       </c>
-      <c r="B91" s="29">
+      <c r="B91" s="25">
         <v>46137</v>
       </c>
-      <c r="C91" s="32">
+      <c r="C91" s="28">
         <v>830</v>
       </c>
-      <c r="D91" s="32" t="s">
+      <c r="D91" s="28" t="s">
         <v>33</v>
       </c>
       <c r="E91" t="s">
@@ -4910,14 +4910,14 @@
       <c r="G91" t="s">
         <v>68</v>
       </c>
-      <c r="H91" s="30">
+      <c r="H91" s="26">
         <v>520000</v>
       </c>
-      <c r="I91" s="44">
+      <c r="I91" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>260000</v>
       </c>
-      <c r="J91" s="46">
+      <c r="J91" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>13</v>
       </c>
@@ -4928,18 +4928,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92">
         <f t="shared" si="2"/>
         <v>75</v>
       </c>
-      <c r="B92" s="29">
+      <c r="B92" s="25">
         <v>46137</v>
       </c>
-      <c r="C92" s="32">
+      <c r="C92" s="28">
         <v>289</v>
       </c>
-      <c r="D92" s="32" t="s">
+      <c r="D92" s="28" t="s">
         <v>213</v>
       </c>
       <c r="E92" t="s">
@@ -4951,14 +4951,14 @@
       <c r="G92" t="s">
         <v>137</v>
       </c>
-      <c r="H92" s="30">
+      <c r="H92" s="26">
         <v>320000</v>
       </c>
-      <c r="I92" s="44">
+      <c r="I92" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>160000</v>
       </c>
-      <c r="J92" s="46">
+      <c r="J92" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>8</v>
       </c>
@@ -4969,18 +4969,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93">
         <f t="shared" si="2"/>
         <v>76</v>
       </c>
-      <c r="B93" s="29">
+      <c r="B93" s="25">
         <v>46137</v>
       </c>
-      <c r="C93" s="32">
+      <c r="C93" s="28">
         <v>26</v>
       </c>
-      <c r="D93" s="32" t="s">
+      <c r="D93" s="28" t="s">
         <v>60</v>
       </c>
       <c r="E93" t="s">
@@ -4992,14 +4992,14 @@
       <c r="G93" t="s">
         <v>216</v>
       </c>
-      <c r="H93" s="30">
+      <c r="H93" s="26">
         <v>240000</v>
       </c>
-      <c r="I93" s="44">
+      <c r="I93" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>120000</v>
       </c>
-      <c r="J93" s="46">
+      <c r="J93" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>6</v>
       </c>
@@ -5010,18 +5010,18 @@
         <v>217</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94">
         <f t="shared" si="2"/>
         <v>77</v>
       </c>
-      <c r="B94" s="29">
+      <c r="B94" s="25">
         <v>46137</v>
       </c>
-      <c r="C94" s="32">
+      <c r="C94" s="28">
         <v>318</v>
       </c>
-      <c r="D94" s="32" t="s">
+      <c r="D94" s="28" t="s">
         <v>33</v>
       </c>
       <c r="E94" t="s">
@@ -5033,14 +5033,14 @@
       <c r="G94" t="s">
         <v>220</v>
       </c>
-      <c r="H94" s="30">
+      <c r="H94" s="26">
         <v>2080000</v>
       </c>
-      <c r="I94" s="44">
+      <c r="I94" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>1040000</v>
       </c>
-      <c r="J94" s="46">
+      <c r="J94" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>52</v>
       </c>
@@ -5051,18 +5051,18 @@
         <v>81</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95">
         <f t="shared" si="2"/>
         <v>78</v>
       </c>
-      <c r="B95" s="29">
+      <c r="B95" s="25">
         <v>46137</v>
       </c>
-      <c r="C95" s="32">
+      <c r="C95" s="28">
         <v>162</v>
       </c>
-      <c r="D95" s="32" t="s">
+      <c r="D95" s="28" t="s">
         <v>110</v>
       </c>
       <c r="E95" t="s">
@@ -5074,14 +5074,14 @@
       <c r="G95" t="s">
         <v>222</v>
       </c>
-      <c r="H95" s="30">
+      <c r="H95" s="26">
         <v>200000</v>
       </c>
-      <c r="I95" s="44">
+      <c r="I95" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>100000</v>
       </c>
-      <c r="J95" s="46">
+      <c r="J95" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>5</v>
       </c>
@@ -5092,18 +5092,18 @@
         <v>223</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96">
         <f t="shared" si="2"/>
         <v>79</v>
       </c>
-      <c r="B96" s="29">
+      <c r="B96" s="25">
         <v>46137</v>
       </c>
-      <c r="C96" s="32">
+      <c r="C96" s="28">
         <v>169</v>
       </c>
-      <c r="D96" s="32" t="s">
+      <c r="D96" s="28" t="s">
         <v>224</v>
       </c>
       <c r="E96" t="s">
@@ -5115,14 +5115,14 @@
       <c r="G96" t="s">
         <v>225</v>
       </c>
-      <c r="H96" s="30">
+      <c r="H96" s="26">
         <v>280000</v>
       </c>
-      <c r="I96" s="44">
+      <c r="I96" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>140000</v>
       </c>
-      <c r="J96" s="46">
+      <c r="J96" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>7</v>
       </c>
@@ -5133,17 +5133,17 @@
         <v>226</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>80</v>
       </c>
-      <c r="B97" s="29">
+      <c r="B97" s="25">
         <v>46137</v>
       </c>
-      <c r="C97" s="32">
+      <c r="C97" s="28">
         <v>169</v>
       </c>
-      <c r="D97" s="32" t="s">
+      <c r="D97" s="28" t="s">
         <v>224</v>
       </c>
       <c r="E97" t="s">
@@ -5155,14 +5155,14 @@
       <c r="G97" t="s">
         <v>225</v>
       </c>
-      <c r="H97" s="30">
+      <c r="H97" s="26">
         <v>240000</v>
       </c>
-      <c r="I97" s="44">
+      <c r="I97" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>120000</v>
       </c>
-      <c r="J97" s="46">
+      <c r="J97" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>6</v>
       </c>
@@ -5173,17 +5173,17 @@
         <v>226</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>81</v>
       </c>
-      <c r="B98" s="29">
+      <c r="B98" s="25">
         <v>46139</v>
       </c>
-      <c r="C98" s="32">
+      <c r="C98" s="28">
         <v>246</v>
       </c>
-      <c r="D98" s="32" t="s">
+      <c r="D98" s="28" t="s">
         <v>33</v>
       </c>
       <c r="E98" t="s">
@@ -5195,14 +5195,14 @@
       <c r="G98" t="s">
         <v>228</v>
       </c>
-      <c r="H98" s="30">
+      <c r="H98" s="26">
         <v>1000000</v>
       </c>
-      <c r="I98" s="44">
+      <c r="I98" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>500000</v>
       </c>
-      <c r="J98" s="46">
+      <c r="J98" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>25</v>
       </c>
@@ -5213,17 +5213,17 @@
         <v>49</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>82</v>
       </c>
-      <c r="B99" s="29">
+      <c r="B99" s="25">
         <v>46139</v>
       </c>
-      <c r="C99" s="32">
+      <c r="C99" s="28">
         <v>447</v>
       </c>
-      <c r="D99" s="32" t="s">
+      <c r="D99" s="28" t="s">
         <v>33</v>
       </c>
       <c r="E99" t="s">
@@ -5235,14 +5235,14 @@
       <c r="G99" t="s">
         <v>36</v>
       </c>
-      <c r="H99" s="30">
+      <c r="H99" s="26">
         <v>200000</v>
       </c>
-      <c r="I99" s="44">
+      <c r="I99" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>100000</v>
       </c>
-      <c r="J99" s="46">
+      <c r="J99" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>5</v>
       </c>
@@ -5253,17 +5253,17 @@
         <v>49</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>83</v>
       </c>
-      <c r="B100" s="29">
+      <c r="B100" s="25">
         <v>46139</v>
       </c>
-      <c r="C100" s="32">
+      <c r="C100" s="28">
         <v>445</v>
       </c>
-      <c r="D100" s="32" t="s">
+      <c r="D100" s="28" t="s">
         <v>60</v>
       </c>
       <c r="E100" t="s">
@@ -5275,14 +5275,14 @@
       <c r="G100" t="s">
         <v>231</v>
       </c>
-      <c r="H100" s="30">
+      <c r="H100" s="26">
         <v>200000</v>
       </c>
-      <c r="I100" s="44">
+      <c r="I100" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>100000</v>
       </c>
-      <c r="J100" s="46">
+      <c r="J100" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>5</v>
       </c>
@@ -5293,17 +5293,17 @@
         <v>49</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>84</v>
       </c>
-      <c r="B101" s="29">
+      <c r="B101" s="25">
         <v>46141</v>
       </c>
-      <c r="C101" s="32">
+      <c r="C101" s="28">
         <v>434</v>
       </c>
-      <c r="D101" s="32" t="s">
+      <c r="D101" s="28" t="s">
         <v>33</v>
       </c>
       <c r="E101" t="s">
@@ -5315,14 +5315,14 @@
       <c r="G101" t="s">
         <v>233</v>
       </c>
-      <c r="H101" s="30">
+      <c r="H101" s="26">
         <v>320000</v>
       </c>
-      <c r="I101" s="44">
+      <c r="I101" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>160000</v>
       </c>
-      <c r="J101" s="46">
+      <c r="J101" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>8</v>
       </c>
@@ -5333,17 +5333,17 @@
         <v>109</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>85</v>
       </c>
-      <c r="B102" s="29">
+      <c r="B102" s="25">
         <v>46141</v>
       </c>
-      <c r="C102" s="32">
+      <c r="C102" s="28">
         <v>36</v>
       </c>
-      <c r="D102" s="32" t="s">
+      <c r="D102" s="28" t="s">
         <v>50</v>
       </c>
       <c r="E102" t="s">
@@ -5355,14 +5355,14 @@
       <c r="G102" t="s">
         <v>233</v>
       </c>
-      <c r="H102" s="30">
+      <c r="H102" s="26">
         <v>320000</v>
       </c>
-      <c r="I102" s="44">
+      <c r="I102" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>160000</v>
       </c>
-      <c r="J102" s="46">
+      <c r="J102" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>8</v>
       </c>
@@ -5373,17 +5373,17 @@
         <v>77</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>86</v>
       </c>
-      <c r="B103" s="29">
+      <c r="B103" s="25">
         <v>46141</v>
       </c>
-      <c r="C103" s="32">
+      <c r="C103" s="28">
         <v>343</v>
       </c>
-      <c r="D103" s="32" t="s">
+      <c r="D103" s="28" t="s">
         <v>33</v>
       </c>
       <c r="E103" t="s">
@@ -5395,14 +5395,14 @@
       <c r="G103" t="s">
         <v>233</v>
       </c>
-      <c r="H103" s="30">
+      <c r="H103" s="26">
         <v>320000</v>
       </c>
-      <c r="I103" s="44">
+      <c r="I103" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>160000</v>
       </c>
-      <c r="J103" s="46">
+      <c r="J103" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>8</v>
       </c>
@@ -5413,17 +5413,17 @@
         <v>77</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>87</v>
       </c>
-      <c r="B104" s="29">
+      <c r="B104" s="25">
         <v>46141</v>
       </c>
-      <c r="C104" s="32">
+      <c r="C104" s="28">
         <v>247</v>
       </c>
-      <c r="D104" s="32" t="s">
+      <c r="D104" s="28" t="s">
         <v>33</v>
       </c>
       <c r="E104" t="s">
@@ -5435,14 +5435,14 @@
       <c r="G104" t="s">
         <v>237</v>
       </c>
-      <c r="H104" s="30">
+      <c r="H104" s="26">
         <v>320000</v>
       </c>
-      <c r="I104" s="44">
+      <c r="I104" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>160000</v>
       </c>
-      <c r="J104" s="46">
+      <c r="J104" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>8</v>
       </c>
@@ -5453,17 +5453,17 @@
         <v>77</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>88</v>
       </c>
-      <c r="B105" s="29">
+      <c r="B105" s="25">
         <v>46141</v>
       </c>
-      <c r="C105" s="32">
+      <c r="C105" s="28">
         <v>275</v>
       </c>
-      <c r="D105" s="32" t="s">
+      <c r="D105" s="28" t="s">
         <v>33</v>
       </c>
       <c r="E105" t="s">
@@ -5475,14 +5475,14 @@
       <c r="G105" t="s">
         <v>237</v>
       </c>
-      <c r="H105" s="30">
+      <c r="H105" s="26">
         <v>320000</v>
       </c>
-      <c r="I105" s="44">
+      <c r="I105" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>160000</v>
       </c>
-      <c r="J105" s="46">
+      <c r="J105" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>8</v>
       </c>
@@ -5493,17 +5493,17 @@
         <v>77</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>89</v>
       </c>
-      <c r="B106" s="29">
+      <c r="B106" s="25">
         <v>46141</v>
       </c>
-      <c r="C106" s="32">
+      <c r="C106" s="28">
         <v>436</v>
       </c>
-      <c r="D106" s="32" t="s">
+      <c r="D106" s="28" t="s">
         <v>33</v>
       </c>
       <c r="E106" t="s">
@@ -5515,14 +5515,14 @@
       <c r="G106" t="s">
         <v>237</v>
       </c>
-      <c r="H106" s="30">
+      <c r="H106" s="26">
         <v>320000</v>
       </c>
-      <c r="I106" s="44">
+      <c r="I106" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>160000</v>
       </c>
-      <c r="J106" s="46">
+      <c r="J106" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>8</v>
       </c>
@@ -5533,17 +5533,17 @@
         <v>77</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>90</v>
       </c>
-      <c r="B107" s="29">
+      <c r="B107" s="25">
         <v>46141</v>
       </c>
-      <c r="C107" s="32">
+      <c r="C107" s="28">
         <v>29</v>
       </c>
-      <c r="D107" s="32" t="s">
+      <c r="D107" s="28" t="s">
         <v>60</v>
       </c>
       <c r="E107" t="s">
@@ -5555,14 +5555,14 @@
       <c r="G107" t="s">
         <v>201</v>
       </c>
-      <c r="H107" s="30">
+      <c r="H107" s="26">
         <v>160000</v>
       </c>
-      <c r="I107" s="44">
+      <c r="I107" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>80000</v>
       </c>
-      <c r="J107" s="46">
+      <c r="J107" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>4</v>
       </c>
@@ -5573,18 +5573,18 @@
         <v>77</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108">
         <f>A107+1</f>
         <v>91</v>
       </c>
-      <c r="B108" s="29">
+      <c r="B108" s="25">
         <v>46141</v>
       </c>
-      <c r="C108" s="32">
+      <c r="C108" s="28">
         <v>395</v>
       </c>
-      <c r="D108" s="32" t="s">
+      <c r="D108" s="28" t="s">
         <v>60</v>
       </c>
       <c r="E108" t="s">
@@ -5596,14 +5596,14 @@
       <c r="G108" t="s">
         <v>242</v>
       </c>
-      <c r="H108" s="30">
+      <c r="H108" s="26">
         <v>200000</v>
       </c>
-      <c r="I108" s="44">
+      <c r="I108" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>100000</v>
       </c>
-      <c r="J108" s="46">
+      <c r="J108" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>5</v>
       </c>
@@ -5614,18 +5614,18 @@
         <v>77</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109">
         <f t="shared" ref="A109:A119" si="3">A108+1</f>
         <v>92</v>
       </c>
-      <c r="B109" s="29">
+      <c r="B109" s="25">
         <v>46149</v>
       </c>
-      <c r="C109" s="32">
+      <c r="C109" s="28">
         <v>40</v>
       </c>
-      <c r="D109" s="32" t="s">
+      <c r="D109" s="28" t="s">
         <v>50</v>
       </c>
       <c r="E109" t="s">
@@ -5637,14 +5637,14 @@
       <c r="G109" t="s">
         <v>244</v>
       </c>
-      <c r="H109" s="30">
+      <c r="H109" s="26">
         <v>520000</v>
       </c>
-      <c r="I109" s="44">
+      <c r="I109" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>260000</v>
       </c>
-      <c r="J109" s="46">
+      <c r="J109" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>13</v>
       </c>
@@ -5655,18 +5655,18 @@
         <v>77</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110">
         <f t="shared" si="3"/>
         <v>93</v>
       </c>
-      <c r="B110" s="29">
+      <c r="B110" s="25">
         <v>46148</v>
       </c>
-      <c r="C110" s="32">
+      <c r="C110" s="28">
         <v>425</v>
       </c>
-      <c r="D110" s="32" t="s">
+      <c r="D110" s="28" t="s">
         <v>60</v>
       </c>
       <c r="E110" t="s">
@@ -5678,14 +5678,14 @@
       <c r="G110" t="s">
         <v>246</v>
       </c>
-      <c r="H110" s="30">
+      <c r="H110" s="26">
         <v>200000</v>
       </c>
-      <c r="I110" s="44">
+      <c r="I110" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>100000</v>
       </c>
-      <c r="J110" s="46">
+      <c r="J110" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>5</v>
       </c>
@@ -5696,18 +5696,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111">
         <f t="shared" si="3"/>
         <v>94</v>
       </c>
-      <c r="B111" s="29">
+      <c r="B111" s="25">
         <v>46148</v>
       </c>
-      <c r="C111" s="32">
+      <c r="C111" s="28">
         <v>383</v>
       </c>
-      <c r="D111" s="32" t="s">
+      <c r="D111" s="28" t="s">
         <v>33</v>
       </c>
       <c r="E111" t="s">
@@ -5719,14 +5719,14 @@
       <c r="G111" t="s">
         <v>248</v>
       </c>
-      <c r="H111" s="30">
+      <c r="H111" s="26">
         <v>1040000</v>
       </c>
-      <c r="I111" s="44">
+      <c r="I111" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>520000</v>
       </c>
-      <c r="J111" s="46">
+      <c r="J111" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>26</v>
       </c>
@@ -5737,18 +5737,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112">
         <f t="shared" si="3"/>
         <v>95</v>
       </c>
-      <c r="B112" s="29">
+      <c r="B112" s="25">
         <v>46148</v>
       </c>
-      <c r="C112" s="32">
+      <c r="C112" s="28">
         <v>126</v>
       </c>
-      <c r="D112" s="32" t="s">
+      <c r="D112" s="28" t="s">
         <v>50</v>
       </c>
       <c r="E112" t="s">
@@ -5760,14 +5760,14 @@
       <c r="G112" t="s">
         <v>233</v>
       </c>
-      <c r="H112" s="30">
+      <c r="H112" s="26">
         <v>1160000</v>
       </c>
-      <c r="I112" s="44">
+      <c r="I112" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>580000</v>
       </c>
-      <c r="J112" s="46">
+      <c r="J112" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>29</v>
       </c>
@@ -5778,18 +5778,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113">
         <f t="shared" si="3"/>
         <v>96</v>
       </c>
-      <c r="B113" s="29">
+      <c r="B113" s="25">
         <v>46149</v>
       </c>
-      <c r="C113" s="32">
+      <c r="C113" s="28">
         <v>124</v>
       </c>
-      <c r="D113" s="32" t="s">
+      <c r="D113" s="28" t="s">
         <v>33</v>
       </c>
       <c r="E113" t="s">
@@ -5801,14 +5801,14 @@
       <c r="G113" t="s">
         <v>251</v>
       </c>
-      <c r="H113" s="30">
+      <c r="H113" s="26">
         <v>1040000</v>
       </c>
-      <c r="I113" s="44">
+      <c r="I113" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>520000</v>
       </c>
-      <c r="J113" s="46">
+      <c r="J113" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>26</v>
       </c>
@@ -5819,18 +5819,18 @@
         <v>77</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114">
         <f t="shared" si="3"/>
         <v>97</v>
       </c>
-      <c r="B114" s="29">
+      <c r="B114" s="25">
         <v>46149</v>
       </c>
-      <c r="C114" s="32">
+      <c r="C114" s="28">
         <v>778</v>
       </c>
-      <c r="D114" s="32" t="s">
+      <c r="D114" s="28" t="s">
         <v>33</v>
       </c>
       <c r="E114" t="s">
@@ -5842,14 +5842,14 @@
       <c r="G114" t="s">
         <v>137</v>
       </c>
-      <c r="H114" s="30">
+      <c r="H114" s="26">
         <v>4000000</v>
       </c>
-      <c r="I114" s="44">
+      <c r="I114" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>2000000</v>
       </c>
-      <c r="J114" s="46">
+      <c r="J114" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>100</v>
       </c>
@@ -5860,18 +5860,18 @@
         <v>77</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115">
         <f t="shared" si="3"/>
         <v>98</v>
       </c>
-      <c r="B115" s="29">
+      <c r="B115" s="25">
         <v>46148</v>
       </c>
-      <c r="C115" s="32" t="s">
+      <c r="C115" s="28" t="s">
         <v>253</v>
       </c>
-      <c r="D115" s="32" t="s">
+      <c r="D115" s="28" t="s">
         <v>254</v>
       </c>
       <c r="E115" t="s">
@@ -5883,14 +5883,14 @@
       <c r="G115" t="s">
         <v>257</v>
       </c>
-      <c r="H115" s="30">
+      <c r="H115" s="26">
         <v>120000</v>
       </c>
-      <c r="I115" s="44">
+      <c r="I115" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>60000</v>
       </c>
-      <c r="J115" s="46">
+      <c r="J115" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>3</v>
       </c>
@@ -5901,18 +5901,18 @@
         <v>199</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116">
         <f t="shared" si="3"/>
         <v>99</v>
       </c>
-      <c r="B116" s="29">
+      <c r="B116" s="25">
         <v>46151</v>
       </c>
-      <c r="C116" s="32">
+      <c r="C116" s="28">
         <v>206</v>
       </c>
-      <c r="D116" s="32" t="s">
+      <c r="D116" s="28" t="s">
         <v>33</v>
       </c>
       <c r="E116" t="s">
@@ -5924,14 +5924,14 @@
       <c r="G116" t="s">
         <v>251</v>
       </c>
-      <c r="H116" s="30">
+      <c r="H116" s="26">
         <v>1040000</v>
       </c>
-      <c r="I116" s="44">
+      <c r="I116" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>520000</v>
       </c>
-      <c r="J116" s="46">
+      <c r="J116" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>26</v>
       </c>
@@ -5942,18 +5942,18 @@
         <v>77</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="B117" s="29">
+      <c r="B117" s="25">
         <v>46160</v>
       </c>
-      <c r="C117" s="32">
+      <c r="C117" s="28">
         <v>38</v>
       </c>
-      <c r="D117" s="32" t="s">
+      <c r="D117" s="28" t="s">
         <v>259</v>
       </c>
       <c r="E117" t="s">
@@ -5965,14 +5965,14 @@
       <c r="G117" t="s">
         <v>58</v>
       </c>
-      <c r="H117" s="30">
+      <c r="H117" s="26">
         <v>20000000</v>
       </c>
-      <c r="I117" s="44">
+      <c r="I117" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>10000000</v>
       </c>
-      <c r="J117" s="46">
+      <c r="J117" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>500</v>
       </c>
@@ -5983,15 +5983,15 @@
         <v>262</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118">
         <f t="shared" si="3"/>
         <v>101</v>
       </c>
-      <c r="C118" s="32">
+      <c r="C118" s="28">
         <v>482</v>
       </c>
-      <c r="D118" s="32" t="s">
+      <c r="D118" s="28" t="s">
         <v>213</v>
       </c>
       <c r="E118" t="s">
@@ -6000,12 +6000,12 @@
       <c r="G118" t="s">
         <v>263</v>
       </c>
-      <c r="H118" s="30"/>
-      <c r="I118" s="44">
+      <c r="H118" s="26"/>
+      <c r="I118" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>0</v>
       </c>
-      <c r="J118" s="46">
+      <c r="J118" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>0</v>
       </c>
@@ -6013,18 +6013,18 @@
         <v>64</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119">
         <f t="shared" si="3"/>
         <v>102</v>
       </c>
-      <c r="B119" s="29">
+      <c r="B119" s="25">
         <v>46160</v>
       </c>
-      <c r="C119" s="32">
+      <c r="C119" s="28">
         <v>167</v>
       </c>
-      <c r="D119" s="32" t="s">
+      <c r="D119" s="28" t="s">
         <v>110</v>
       </c>
       <c r="E119" t="s">
@@ -6036,14 +6036,14 @@
       <c r="G119" t="s">
         <v>265</v>
       </c>
-      <c r="H119" s="30">
+      <c r="H119" s="26">
         <v>320000</v>
       </c>
-      <c r="I119" s="44">
+      <c r="I119" s="40">
         <f>Table13[[#This Row],[Installment]]/2</f>
         <v>160000</v>
       </c>
-      <c r="J119" s="46">
+      <c r="J119" s="42">
         <f>Table13[[#This Row],[Investment Value]]/20000</f>
         <v>8</v>
       </c>
